--- a/tests/bahan/serapan.xlsx
+++ b/tests/bahan/serapan.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serapan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lampiran Kosong" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +473,38 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Perjalanan dinas</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D5">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>